--- a/output/pdf_financials_xlsx/HME.xlsx
+++ b/output/pdf_financials_xlsx/HME.xlsx
@@ -5868,16 +5868,16 @@
         <v>4.543065</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>4.720591</v>
+        <v>0.285079</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.5072759999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.214325</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.574789</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -7385,31 +7385,31 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.527522</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-1.57415</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1.889546</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.410477</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.258484</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-3.531956</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-2.726735</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-7.716018</v>
       </c>
       <c r="M118" s="1" t="inlineStr">
         <is>
@@ -7417,16 +7417,16 @@
         </is>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-1.002</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-2.629</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-10.296</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-2.066</v>
       </c>
     </row>
     <row r="119">
@@ -17602,7 +17602,11 @@
           <t>Share‐based payment reserve 12(b)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -19066,7 +19070,11 @@
           <t>Share‐based payment reserve 12(c) 2,214,325</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -20028,7 +20036,11 @@
           <t>Share-based payment reserve 12(c)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -21750,7 +21762,11 @@
           <t>Exploration and evaluation expense 8</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -22594,7 +22610,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -26054,7 +26074,11 @@
           <t>Exploration and evaluation expense</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -26890,7 +26914,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HME.xlsx
+++ b/output/pdf_financials_xlsx/HME.xlsx
@@ -987,16 +987,16 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>37.221</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>36.135</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>35.582</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>38.841</v>
       </c>
     </row>
     <row r="11">
@@ -1058,16 +1058,16 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>72.224</v>
+        <v>35.003</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>67.702</v>
+        <v>31.567</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>79.70999999999999</v>
+        <v>44.128</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>77.11499999999999</v>
+        <v>38.274</v>
       </c>
     </row>
     <row r="12">
@@ -1090,7 +1090,7 @@
         <v>0.004545</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.000865</v>
+        <v>-0.000865</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.121</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
         <v>-2.977455</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.452744</v>
+        <v>-0.451014</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.942665</v>
@@ -2155,7 +2155,7 @@
         <v>29.66</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>32.466</v>
+        <v>32.587</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>43.526</v>
@@ -2245,7 +2245,7 @@
         <v>-2.977455</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.452744</v>
+        <v>-0.451014</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0.942665</v>
@@ -2277,7 +2277,7 @@
         <v>37.544</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>41.483</v>
+        <v>41.604</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>53.772</v>
@@ -2348,7 +2348,7 @@
         <v>51.98272042534337</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>61.27293137573484</v>
+        <v>61.45165578564887</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>67.4595408355288</v>
@@ -9062,7 +9062,11 @@
           <t>Reclamation deposits 10</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -11558,7 +11562,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13978,7 +13986,11 @@
           <t>Reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15302,7 +15314,11 @@
           <t>Reclamation deposits 115,535</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -15686,7 +15702,11 @@
           <t>Reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -18182,7 +18202,11 @@
           <t>Reclamation deposits 9 100,535</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -20712,7 +20736,11 @@
           <t>Reclamation Deposits</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E131" s="5" t="n">
         <v>0.056441</v>
       </c>
@@ -33308,7 +33336,11 @@
           <t>Reclamation deposits 51,442</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -37366,7 +37398,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -41792,7 +41828,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -46772,7 +46808,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -51794,7 +51830,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -53596,7 +53632,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -55488,7 +55524,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -57320,7 +57356,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -59034,7 +59070,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -59132,7 +59168,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">

--- a/output/pdf_financials_xlsx/HME.xlsx
+++ b/output/pdf_financials_xlsx/HME.xlsx
@@ -1148,19 +1148,19 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>0.000182</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.005623</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.040459</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.276347</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.571359</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>-0</v>
@@ -2120,19 +2120,19 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.977455</v>
+        <v>-2.977637</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.451014</v>
+        <v>-0.445391</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.942665</v>
+        <v>0.983124</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.907495</v>
+        <v>-1.631148</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-6.668915</v>
+        <v>-6.097556</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-2.680647</v>
@@ -2242,19 +2242,19 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.977455</v>
+        <v>-2.977637</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.451014</v>
+        <v>-0.445391</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.942665</v>
+        <v>0.983124</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.453494</v>
+        <v>3.729841</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.54821</v>
+        <v>-0.976851</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.116698</v>
@@ -7019,7 +7019,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.004905</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -37204,7 +37204,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -53822,7 +53826,11 @@
           <t>Net finance expenses $</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -55808,7 +55816,11 @@
           <t>Net finance expenses $ 195,776 $</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
@@ -57646,7 +57658,11 @@
           <t>Net finance expenses $ 40,459 $</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -58588,7 +58604,11 @@
           <t>Net finance expense 10</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr"/>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E529" t="inlineStr">
         <is>
           <t>-</t>
@@ -59452,7 +59472,11 @@
           <t>Net finance expenses $</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
